--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7665a42965174156"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8113589410444105"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8113589410444105"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R02ed2f17d89f4294"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R02ed2f17d89f4294"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R93843279671e4738"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R93843279671e4738"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re5f5aeee73e84347"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re5f5aeee73e84347"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R24f34ea0db0f4649"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R24f34ea0db0f4649"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5bc88b0df29b4282"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5bc88b0df29b4282"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3b20103ec58a4854"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3b20103ec58a4854"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R49a365fb64674457"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R49a365fb64674457"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3dc1cb85d1524e80"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3dc1cb85d1524e80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5a1618af008046ed"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5a1618af008046ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6a091c4b714f4daf"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6a091c4b714f4daf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9a450666f1544deb"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9a450666f1544deb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8fecef3255ec4624"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8fecef3255ec4624"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R21474318a6454f1d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R21474318a6454f1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R43c5daecc2d34399"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R43c5daecc2d34399"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd5b03b1d4d7b42fc"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd5b03b1d4d7b42fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf85beff3e5344af3"/>
   </x:sheets>
 </x:workbook>
 </file>
